--- a/output/decision_makers.xlsx
+++ b/output/decision_makers.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -551,32 +551,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adam Wheeler</t>
+          <t>Kevin Fennell</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>EVP, Chief Financial Officer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/adam-wheeler-4a7a031b</t>
+          <t>http://linkedin.com/in/kevin-fennell-8188554</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>adam.wheeler@clarionpartners.com</t>
+          <t>kevin.fennell@broadstone.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,7 +592,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -605,12 +605,12 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,32 +651,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bohdy Hedgcock</t>
+          <t>Matt Sauer 175b1317</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Matt Sauer - Director - Broadstone Net Lease, Inc. | LinkedIn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/bohdy-hedgcock-4084554</t>
+          <t>https://linkedin.com/in/matt-sauer-175b1317</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>bohdy.hedgcock@clarionpartners.com</t>
+          <t>matt.sauer@broadstone.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -692,7 +692,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -705,14 +705,14 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>Rochester</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>United States</t>
@@ -720,7 +720,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -741,7 +741,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -751,32 +751,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brent Jenkins</t>
+          <t>Ryan Albano</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>President and COO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/bejenkins</t>
+          <t>http://linkedin.com/in/ryan-albano-51890111</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>brent.jenkins@clarionpartners.com</t>
+          <t>ryan.albano@broadstone.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -805,7 +805,7 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -851,32 +851,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brett Kahn</t>
+          <t>Jennielobrien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Jennie O'Brien, CPA - SVP, Chief Accounting Officer at Broadstone Net Lease - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/brett-kahn-5338993</t>
+          <t>https://linkedin.com/in/jennielobrien</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>brett.kahn@clarionpartners.com</t>
+          <t>jennie.obrien@broadstone.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -892,7 +892,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -905,12 +905,12 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -920,11 +920,11 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -941,7 +941,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brian Watkins</t>
+          <t>Lynnecody</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Lynne Cody - Director, Due Diligence &amp; Transactions - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/brian-watkins-a02a9210</t>
+          <t>https://linkedin.com/in/lynnecody</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>brian.watkins@clarionpartners.com</t>
+          <t>lynne.cody@broadstone.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1005,14 +1005,14 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>Mendon</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>United States</t>
@@ -1020,11 +1020,11 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1051,32 +1051,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elliott Byers</t>
+          <t>Vinh Nguyen 58375a103</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Vinh Nguyen - Director, Information Technology at Broadstone Net ...</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/elliott-byers-7a93114b</t>
+          <t>https://linkedin.com/in/vinh-nguyen-58375a103</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>elliott.byers@clarionpartners.com</t>
+          <t>vinh.nguyen@broadstone.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1092,7 +1092,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1105,12 +1105,12 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fairport</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1120,11 +1120,11 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1141,7 +1141,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Evans Anderson</t>
+          <t>Erica Walter Arm A0076b169</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Erica Walter, ARM - -- - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/evans-k-anderson-jr-4522609</t>
+          <t>https://linkedin.com/in/erica-walter-arm-a0076b169</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>evans.anderson@clarionpartners.com</t>
+          <t>erica.walter@broadstone.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1205,14 +1205,14 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>Rochester</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>United States</t>
@@ -1220,11 +1220,11 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glenn Johnson</t>
+          <t>Ryan Albano 51890111</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Ryan Albano - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/glenn-johnson-boston</t>
+          <t>https://linkedin.com/in/ryan-albano-51890111</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>glenn.johnson@clarionpartners.com</t>
+          <t>ryan.albano@broadstone.com</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1305,12 +1305,12 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1341,7 +1341,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1351,32 +1351,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heather Hopkins</t>
+          <t>Laura Roethel 26381a149</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fund CFO</t>
+          <t>Laura Roethel - Broadstone Net Lease, Inc. - LinkedIn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/heather-hopkins-217a0bb</t>
+          <t>https://linkedin.com/in/laura-roethel-26381a149</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>heather.hopkins@clarionpartners.com</t>
+          <t>laura.roethel@broadstone.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1392,7 +1392,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Garrison</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1420,11 +1420,11 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1441,7 +1441,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1451,32 +1451,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jason Glasser</t>
+          <t>Matthew Morsch B4b02930</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Matthew Morsch - Senior Manager, Property Management, Industrial at Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/jason-glasser-52a73ab6</t>
+          <t>https://linkedin.com/in/matthew-morsch-b4b02930</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>jason.glasser@clarionpartners.com</t>
+          <t>matthew.morsch@broadstone.com</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1505,14 +1505,14 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>Rochester</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>United States</t>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>John Deberadinis</t>
+          <t>Michael Caruso 17537083</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Managing Director, Fund CFO</t>
+          <t>Michael Caruso - Broadstone Net Lease, Inc. - LinkedIn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/john-deberadinis-782b4942</t>
+          <t>https://linkedin.com/in/michael-caruso-17537083</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>john.deberadinis@clarionpartners.com</t>
+          <t>michael.caruso@broadstone.com</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1592,7 +1592,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1605,14 +1605,14 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>Rochester</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>United States</t>
@@ -1620,11 +1620,11 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Josh Kane</t>
+          <t>Sam Delemos 722b1722</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Sam DeLemos - Real Estate Investment Professional - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/josh-kane-45361017</t>
+          <t>https://linkedin.com/in/sam-delemos-722b1722</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>josh.kane@clarionpartners.com</t>
+          <t>sam.delemos@broadstone.com</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1692,7 +1692,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1705,12 +1705,12 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1720,11 +1720,11 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1751,32 +1751,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karen Kasteel</t>
+          <t>Christina Ingerson 63149414</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Christina Ingerson - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/karen-kasteel</t>
+          <t>https://linkedin.com/in/christina-ingerson-63149414</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>karen.kasteel@clarionpartners.com</t>
+          <t>christina.ingerson@broadstone.com</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1792,7 +1792,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1805,14 +1805,14 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>Rochester</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>United States</t>
@@ -1820,15 +1820,15 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1851,32 +1851,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kevin Bishop</t>
+          <t>John Callan 83265954</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>John Callan - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/kevin-bishop-cfa-baba934</t>
+          <t>https://linkedin.com/in/john-callan-83265954</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>kevin.bishop@clarionpartners.com</t>
+          <t>john.callan@broadstone.com</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1892,7 +1892,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1905,12 +1905,12 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1920,15 +1920,15 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1951,32 +1951,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/clarion-partners-llc</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Khalid Rashid</t>
+          <t>Kevin Fennell 8188554</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Kevin Fennell - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/krashid2008</t>
+          <t>https://linkedin.com/in/kevin-fennell-8188554</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>khalid.rashid@clarionpartners.com</t>
+          <t>kevin.fennell@broadstone.com</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1992,7 +1992,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2005,12 +2005,12 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2020,15 +2020,15 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>tavily</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">

--- a/output/decision_makers.xlsx
+++ b/output/decision_makers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -556,27 +556,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Eric Rothman Cfa 02561710</t>
+          <t>Jennielobrien</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Eric Rothman, CFA - Portfolio Manager</t>
+          <t>SVP, Chief Accounting Officer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/eric-rothman-cfa-02561710</t>
+          <t>https://linkedin.com/in/jennielobrien</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Portfolio Manager</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -615,7 +615,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -625,27 +625,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rjosephlaw</t>
+          <t>Maxim Sertl 726775a6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Joseph Law - CFO</t>
+          <t>Director, Underwriting &amp; Research</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/rjosephlaw</t>
+          <t>https://linkedin.com/in/maxim-sertl-726775a6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -684,7 +684,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -694,27 +694,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Richard Gorsky Ba87859</t>
+          <t>Vinh Nguyen 58375a103</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Richard Gorsky - Managing Director</t>
+          <t>Director, Information Technology</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/richard-gorsky-ba87859</t>
+          <t>https://linkedin.com/in/vinh-nguyen-58375a103</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -753,7 +753,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -763,27 +763,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chad Burkhardt B095a5b9</t>
+          <t>Ryan Albano 51890111</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chad Burkhardt - Managing Director, CenterSquare Investment ...</t>
+          <t>Albano</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/chad-burkhardt-b095a5b9</t>
+          <t>https://linkedin.com/in/ryan-albano-51890111</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -822,7 +822,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -832,27 +832,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deborah Considine</t>
+          <t>Amy Tait 34b9bb22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deborah Considine - Managing Director, Capital Markets ... - LinkedIn</t>
+          <t>Retired Founder/Chair/CEO at Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/deborah-considine</t>
+          <t>https://linkedin.com/in/amy-tait-34b9bb22</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -901,27 +901,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Victoriamadrid</t>
+          <t>Andrea Paquin Cpp Cebs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Victoria Bocanegra - Vice President, CenterSquare Investment ...</t>
+          <t>Manager, Payroll &amp; Benefits</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/victoriamadrid</t>
+          <t>https://linkedin.com/in/andrea-paquin-cpp-cebs-b1209166</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -960,7 +960,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -970,27 +970,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gregory Stevens A8a3b321</t>
+          <t>Matthew Morsch B4b02930</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gregory Stevens - CenterSquare Investment Management - LinkedIn</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/gregory-stevens-a8a3b321</t>
+          <t>https://linkedin.com/in/matthew-morsch-b4b02930</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1039,27 +1039,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Melissa Grady 41649b100</t>
+          <t>Michael Caruso 17537083</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Melissa Grady - CenterSquare Investment Management - LinkedIn</t>
+          <t>Senior Vice President, Underwriting &amp; Strategy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/melissa-grady-41649b100</t>
+          <t>https://linkedin.com/in/michael-caruso-17537083</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1108,27 +1108,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Todd Briddell</t>
+          <t>Andrew Ritz 2a3053202</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Todd Briddell - Chief Executive Officer - LinkedIn</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/todd-briddell</t>
+          <t>https://linkedin.com/in/andrew-ritz-2a3053202</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>CIO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adam Schreiner 333515</t>
+          <t>Benjaminbills</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Adam Schreiner - CenterSquare Investment Management | LinkedIn</t>
+          <t>Ben Bills</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/adam-schreiner-333515</t>
+          <t>https://linkedin.com/in/benjaminbills</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1219,11 +1219,11 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1246,27 +1246,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rogoldstein</t>
+          <t>Christina Ingerson 63149414</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rob Goldstein, CFA - Portfolio Manager</t>
+          <t>Ingerson</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/rogoldstein</t>
+          <t>https://linkedin.com/in/christina-ingerson-63149414</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1288,16 +1288,16 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Portfolio Manager</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1315,27 +1315,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Scott Maguire Cfa Caia</t>
+          <t>Kevin Fennell 8188554</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Scott Maguire, CFA, CAIA - CenterSquare Investment Management</t>
+          <t>Fennell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/scott-maguire-cfa-caia-8547153</t>
+          <t>https://linkedin.com/in/kevin-fennell-8188554</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1384,27 +1384,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Michael Brophy 5b7417137</t>
+          <t>Lalvarez320</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Michael Brophy - Chief Compliance Officer</t>
+          <t>Luz Alvarez</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/michael-brophy-5b7417137</t>
+          <t>https://linkedin.com/in/lalvarez320</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1453,27 +1453,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Christina Van Beelen 38472b9</t>
+          <t>Laurie Hawkes 2411a612</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Christina van Beelen - Alternative Investment Leader | Global Product and Distribution Strategy | Growth and Innovation | Board Member | Advisor - Stealth-Mode | Hedge Funds &amp; AI-Driven Technology</t>
+          <t>Hawkes</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/christina-van-beelen-38472b9</t>
+          <t>https://linkedin.com/in/laurie-hawkes-2411a612</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CenterSquare Investment Management</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1522,27 +1522,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/centersquare/mycompany/verification/</t>
+          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://centersquare.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ericreuben</t>
+          <t>Matt Sauer 175b1317</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eric Reuben - Centersquare Investment Management - LinkedIn</t>
+          <t>Sauer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ericreuben</t>
+          <t>https://linkedin.com/in/matt-sauer-175b1317</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1578,6 +1578,3663 @@
       </c>
       <c r="Y16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Andrew Connolly 0953a822</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/andrew-connolly-0953a822</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>100</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Brian Mcclean A9b12157</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Director Property Management</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/brian-mcclean-a9b12157</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>100</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Don Edwards A3078544</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Senior Director Asset Management</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/don-edwards-a3078544</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>100</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Joanne Morano 29437137</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Director of Property Management</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/joanne-morano-29437137</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>100</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sae Ra Park Mba</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Director of Tax</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sae-ra-park-mba-mbt-cpa-49096953</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>100</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Susan Epstein 6aa4006</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Director of Legal Affairs</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/susan-epstein-6aa4006</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>100</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Jack Dimartino 909a4b26</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Former Director of Engineering</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jack-dimartino-909a4b26</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>95</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Thomas Golden 96268a27</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vice President, Development</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/thomas-golden-96268a27</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>90</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mitchell Hersh 2a0397b</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>President &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mitchell-hersh-2a0397b</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>85</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bill Keys 66654aab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>engineering</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/bill-keys-66654aab</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>70</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Florence Schmitt 60584a41</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Property Manager at Mack-Cali Realty Corporation</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/florence-schmitt-60584a41</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>70</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Gary Wagner B2702657</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vice President and Senior Associate General Counsel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/gary-wagner-b2702657</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>70</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Giovanni Benavides 794aa95</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Property Manager</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/giovanni-benavides-794aa95</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>70</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Glenn Baker 53008036</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Property Manager</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/glenn-baker-53008036</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>70</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mack-Cali Realty</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.mack-cali.com</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Magdi Ali 303b3a11b</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>realtor</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/magdi-ali-303b3a11b</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>70</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Luke Castanien 0872394</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Senior Regional Director</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/luke-castanien-0872394</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>75</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mason Berger 78b19327b</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mason-berger-78b19327b</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>70</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Mark Pillor A7586927</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Senior Sales Director</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mark-pillor-a7586927</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>65</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Scott Belval 9a726110</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Senior Sales Director</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/scott-belval-9a726110</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>65</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Angelabarbera</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Managing Director, National Accounts</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/angelabarbera</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>55</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Curano</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Regional Sales Director</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/curano</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>55</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Micahjordan</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Senior Director, National Accounts</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/micahjordan</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>55</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NexPoint Real Estate Finance</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nexpoint</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.nexpoint.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Scott Johnson 75230</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/scott-johnson-75230</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>55</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Dave Holeman 2728b614</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dave-holeman-2728b614</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>100</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Made Setiawan 30188266</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Director of Credit and Collections</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/made-setiawan-30188266</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>100</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Mike Parrish A2b95488</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Parrish</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mike-parrish-a2b95488</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>100</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Paul Meekey A7972413</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Director of Managed Parternships</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/paul-meekey-a7972413</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>100</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Matthew Okmin 1508015</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Okmin</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/matthew-okmin-1508015</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>90</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Melanie Richards 9a23107</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Property Manager</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/melanie-richards-9a23107</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>80</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Camille Patterson Ccim 83221519</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Patterson, CCIM</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/camille-patterson-ccim-83221519</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>70</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Daniel Figard 650a909a</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Figard</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/daniel-figard-650a909a</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>70</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>David Mordy 781479203</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mordy</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/david-mordy-781479203</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>70</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>David Spagnolo 8a753b14</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spagnolo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/david-spagnolo-8a753b14</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>70</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ibrahim Mhawesh</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ibrahim-mhawesh</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>70</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mark Cervantes A1207630</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Cervantes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mark-cervantes-a1207630</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>70</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Scott Hogan A7540911</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Hogan</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/scott-hogan-a7540911</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>70</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ted Zeck 3b036713</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Retired CPA, now just walking and drinking Leinie’s</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ted-zeck-3b036713</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>70</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Whitestone REIT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>REIT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whitestone-reit</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.whitestonereit.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Tim Ng 642b3a7</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/tim-ng-642b3a7</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>70</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Brad Butler 898a847</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Experienced VP Regional Director | Real Estate Leasing</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/brad-butler-898a847</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>100</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Doug Himmel</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Director of Leasing</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/doug-himmel</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>100</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Jeffrey L 584a452</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vice President - Regional Director Florida</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jeffrey-l-584a452</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>100</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Wesrudes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Director Of Leasing</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/wesrudes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>100</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Chris Eckerd Cpm 435a20a8</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SVP</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/chris-eckerd-cpm-435a20a8</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>95</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Anthony Pascale Jr</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Director of Financial Reporting</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/anthony-pascale-jr</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>85</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Erin Grandys</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Property Manager skilled in Facility Management and Property Management</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/erin-grandys</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>70</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>John Beale 810340104</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Senior Property Manager</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/john-beale-810340104</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>70</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Kevin Ault</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/kevin-ault</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>70</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Lisa Grace 272121111</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Manager of Lease Administrator and Accounts Recievable</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/lisa-grace-272121111</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>70</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Michael Gervasio 658453a5</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Senior Vice President</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/michael-gervasio-658453a5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>70</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Mikaela Sherbakov</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Senior Corporate Accountant</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mikaela-sherbakov</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>70</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Stephanpahides</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SVP &amp; General Counsel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/stephanpahides</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>65</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Edgar Gaba B643a765</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gaba</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/edgar-gaba-b643a765</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>60</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Workspace Property Trust</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/workspace-property-trust</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.workspacept.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Francis X Shea 904361116</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Construction &amp; Development Executive</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/francis-x-shea-904361116</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>tavily</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>60</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/decision_makers.xlsx
+++ b/output/decision_makers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y69"/>
+  <dimension ref="A1:Y63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -556,27 +556,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jennielobrien</t>
+          <t>Adam Larson</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SVP, Chief Accounting Officer</t>
+          <t>CFO at Cottonwood Communities</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/jennielobrien</t>
+          <t>https://linkedin.com/in/adam-larson-8a77272</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -625,27 +625,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maxim Sertl 726775a6</t>
+          <t>Paul Fredenberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Director, Underwriting &amp; Research</t>
+          <t>Chief Investment Officer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/maxim-sertl-726775a6</t>
+          <t>https://linkedin.com/in/paul-fredenberg-a42a661</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CIO</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -684,7 +684,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -694,27 +694,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vinh Nguyen 58375a103</t>
+          <t>Enzio Cassinis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Director, Information Technology</t>
+          <t>President at Cottonwood Communities</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/vinh-nguyen-58375a103</t>
+          <t>https://linkedin.com/in/enzio-cassinis-7a708462</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -753,7 +753,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -763,27 +763,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ryan Albano 51890111</t>
+          <t>Michelle Langer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albano</t>
+          <t>Senior Vice President of Capital Markets</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ryan-albano-51890111</t>
+          <t>https://linkedin.com/in/michelle-langer-4761534</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -822,7 +822,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -832,27 +832,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Amy Tait 34b9bb22</t>
+          <t>Graeme Fraser</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Retired Founder/Chair/CEO at Broadstone Net Lease</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/amy-tait-34b9bb22</t>
+          <t>https://linkedin.com/in/graememfraser</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -891,7 +891,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -901,27 +901,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Andrea Paquin Cpp Cebs</t>
+          <t>John West</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manager, Payroll &amp; Benefits</t>
+          <t>CEO at Cottonwood Partners</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/andrea-paquin-cpp-cebs-b1209166</t>
+          <t>https://linkedin.com/in/john-west-b48546129</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -960,7 +960,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -970,27 +970,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Matthew Morsch B4b02930</t>
+          <t>Kristen Holt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Partner, Director of Operations</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/matthew-morsch-b4b02930</t>
+          <t>https://linkedin.com/in/kristen-holt-33516a228</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1039,27 +1039,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Michael Caruso 17537083</t>
+          <t>Anne Brundige</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Senior Vice President, Underwriting &amp; Strategy</t>
+          <t>Managing Partner at Cottonwood Capital Group</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/michael-caruso-17537083</t>
+          <t>https://linkedin.com/in/anne-brundige-125443167</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1108,27 +1108,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Andrew Ritz 2a3053202</t>
+          <t>Mark Green</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Chief Investment Officer at Cottonwood Group</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/andrew-ritz-2a3053202</t>
+          <t>https://linkedin.com/in/greeninvestments</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CIO</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Benjaminbills</t>
+          <t>Mindy V.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Bills</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/benjaminbills</t>
+          <t>https://linkedin.com/in/mindy-v-26035797</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Cottonwood Communities</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1246,27 +1246,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://linkedin.com/company/cottonwood-residential</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.cottonwoodcommunities.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Christina Ingerson 63149414</t>
+          <t>Susan Hallenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ingerson</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/christina-ingerson-63149414</t>
+          <t>https://linkedin.com/in/susan-hallenberg-a685158</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1315,27 +1315,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kevin Fennell 8188554</t>
+          <t>Edsel Vierra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fennell</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/kevin-fennell-8188554</t>
+          <t>https://linkedin.com/in/edsel-vierra</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1384,27 +1384,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lalvarez320</t>
+          <t>Jet Taylor 5b4b30a5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luz Alvarez</t>
+          <t>Retired Managing Director, Investments Division</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/lalvarez320</t>
+          <t>https://linkedin.com/in/jet-taylor-5b4b30a5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1426,11 +1426,11 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1453,27 +1453,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Laurie Hawkes 2411a612</t>
+          <t>Matthew Bacon Cfa 7154b941</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hawkes</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/laurie-hawkes-2411a612</t>
+          <t>https://linkedin.com/in/matthew-bacon-cfa-7154b941</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1495,16 +1495,16 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Broadstone Net Lease</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1522,27 +1522,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/broadstone-net-lease-inc</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.broadstone.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Matt Sauer 175b1317</t>
+          <t>Megan Slocum 856aa910</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sauer</t>
+          <t>Chief Development Officer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/matt-sauer-175b1317</t>
+          <t>https://linkedin.com/in/megan-slocum-856aa910</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Andrew Connolly 0953a822</t>
+          <t>Mwatson04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Senior Director, Development</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/andrew-connolly-0953a822</t>
+          <t>https://linkedin.com/in/mwatson04</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1650,7 +1650,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brian Mcclean A9b12157</t>
+          <t>Robert Duguid A2591b54</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Director Property Management</t>
+          <t>Executive Managing Director Development and Construction</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/brian-mcclean-a9b12157</t>
+          <t>https://linkedin.com/in/robert-duguid-a2591b54</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1729,27 +1729,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Don Edwards A3078544</t>
+          <t>Robert Miller 364b1b7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Senior Director Asset Management</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/don-edwards-a3078544</t>
+          <t>https://linkedin.com/in/robert-miller-364b1b7</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1798,27 +1798,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Joanne Morano 29437137</t>
+          <t>Sherry Long Sowers 73049674</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Director of Property Management</t>
+          <t>Managing Director Investor Relations</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/joanne-morano-29437137</t>
+          <t>https://linkedin.com/in/sherry-long-sowers-73049674</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sae Ra Park Mba</t>
+          <t>Andy Zou Mem 659177133</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Director of Tax</t>
+          <t>Sustainable Design + Urban Development</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/sae-ra-park-mba-mbt-cpa-49096953</t>
+          <t>https://linkedin.com/in/andy-zou-mem-659177133</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1936,27 +1936,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Susan Epstein 6aa4006</t>
+          <t>Todd Williams</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Director of Legal Affairs</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/susan-epstein-6aa4006</t>
+          <t>https://linkedin.com/in/todd--williams</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2005,27 +2005,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jack Dimartino 909a4b26</t>
+          <t>William Whelan 3350617b</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Former Director of Engineering</t>
+          <t>Whelan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/jack-dimartino-909a4b26</t>
+          <t>https://linkedin.com/in/william-whelan-3350617b</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Investor Relations</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2074,27 +2074,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Thomas Golden 96268a27</t>
+          <t>Hillaryhschmidt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vice President, Development</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/thomas-golden-96268a27</t>
+          <t>https://linkedin.com/in/hillaryhschmidt</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Portfolio Manager</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -2133,7 +2133,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2143,27 +2143,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mitchell Hersh 2a0397b</t>
+          <t>James Hochman 134a0b45</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer</t>
+          <t>.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mitchell-hersh-2a0397b</t>
+          <t>https://linkedin.com/in/james-hochman-134a0b45</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2212,27 +2212,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bill Keys 66654aab</t>
+          <t>Radima Smith</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>Executive Assistant to the CEO &amp; CIO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/bill-keys-66654aab</t>
+          <t>https://linkedin.com/in/radima-smith-b8469120</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CIO</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Grubb Properties</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2281,27 +2281,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://www.linkedin.com/company/grubb-properties</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.grubbproperties.com</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Florence Schmitt 60584a41</t>
+          <t>Rishipatel2031</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Property Manager at Mack-Cali Realty Corporation</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/florence-schmitt-60584a41</t>
+          <t>https://linkedin.com/in/rishipatel2031</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -2340,37 +2340,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Industrial Logistics Properties Trust</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>REIT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://linkedin.com/company/industrial-logistics-properties-trust</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.ilptreit.com</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gary Wagner B2702657</t>
+          <t>Lisa Harris Jones 9b5a51147</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vice President and Senior Associate General Counsel</t>
+          <t>Managing Member</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/gary-wagner-b2702657</t>
+          <t>https://linkedin.com/in/lisa-harris-jones-9b5a51147</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2409,37 +2409,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Industrial Logistics Properties Trust</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>REIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://linkedin.com/company/industrial-logistics-properties-trust</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.ilptreit.com</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giovanni Benavides 794aa95</t>
+          <t>Brian Gagne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Property Manager</t>
+          <t>Logistics Properties CIO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/giovanni-benavides-794aa95</t>
+          <t>https://linkedin.com/in/brian-gagne</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2461,16 +2461,16 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CIO</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -2478,37 +2478,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Industrial Logistics Properties Trust</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>REIT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://linkedin.com/company/industrial-logistics-properties-trust</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.ilptreit.com</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Glenn Baker 53008036</t>
+          <t>Johannson Yap A5a00a6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Property Manager</t>
+          <t>Chief Investment Officer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/glenn-baker-53008036</t>
+          <t>https://linkedin.com/in/johannson-yap-a5a00a6</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CIO</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -2547,37 +2547,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mack-Cali Realty</t>
+          <t>Industrial Logistics Properties Trust</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>REIT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/mack-cali-realty-corporation</t>
+          <t>https://linkedin.com/company/industrial-logistics-properties-trust</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.mack-cali.com</t>
+          <t>https://www.ilptreit.com</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Magdi Ali 303b3a11b</t>
+          <t>Marc A Krohn Rpa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>realtor</t>
+          <t>Commercial Real Estate Professional</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/magdi-ali-303b3a11b</t>
+          <t>https://linkedin.com/in/marc-a-krohn-rpa-cpm-75aab912</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -2599,16 +2599,16 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -2616,37 +2616,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Industrial Logistics Properties Trust</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>REIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://linkedin.com/company/industrial-logistics-properties-trust</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.ilptreit.com</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Luke Castanien 0872394</t>
+          <t>Tiffany Sy A846764</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Senior Regional Director</t>
+          <t>Sy</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/luke-castanien-0872394</t>
+          <t>https://linkedin.com/in/tiffany-sy-a846764</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2668,16 +2668,16 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -2685,37 +2685,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Industrial Logistics Properties Trust</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>REIT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://linkedin.com/company/industrial-logistics-properties-trust</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.ilptreit.com</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mason Berger 78b19327b</t>
+          <t>Brendan Mullinix 94b92511</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sales Representative</t>
+          <t>Chief Investment Officer @ LXP Industrial Trust | Logistics Real Estate Acquisitions &amp; Development</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mason-berger-78b19327b</t>
+          <t>https://linkedin.com/in/brendan-mullinix-94b92511</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CIO</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2764,27 +2764,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mark Pillor A7586927</t>
+          <t>Jim Carlston 73578097</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Senior Sales Director</t>
+          <t>Vice President - Director of Investor Reporting</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mark-pillor-a7586927</t>
+          <t>https://linkedin.com/in/jim-carlston-73578097</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2806,11 +2806,11 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -2823,7 +2823,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2833,27 +2833,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Scott Belval 9a726110</t>
+          <t>Kyle Prokup 945b8058</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Senior Sales Director</t>
+          <t>VP Investment Product Strategy</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/scott-belval-9a726110</t>
+          <t>https://linkedin.com/in/kyle-prokup-945b8058</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2875,16 +2875,16 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2902,27 +2902,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Angelabarbera</t>
+          <t>Phil McAlister</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Managing Director, National Accounts</t>
+          <t>Senior Vice President and Head of Research</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/angelabarbera</t>
+          <t>https://linkedin.com/in/phil-mcalister-63436377</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -2961,7 +2961,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2971,27 +2971,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Curano</t>
+          <t>Alexandra Clanton 44087273</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Regional Sales Director</t>
+          <t>Investor Services Specialist – Transfers</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/curano</t>
+          <t>https://linkedin.com/in/alexandra-clanton-44087273</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -3013,16 +3013,16 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -3030,7 +3030,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Micahjordan</t>
+          <t>Mary Jo Wenmouth 36171034</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Senior Director, National Accounts</t>
+          <t>Investment Relations Consultant</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/micahjordan</t>
+          <t>https://linkedin.com/in/mary-jo-wenmouth-36171034</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3082,16 +3082,16 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -3099,7 +3099,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NexPoint Real Estate Finance</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3109,27 +3109,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/nexpoint</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.nexpoint.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Scott Johnson 75230</t>
+          <t>Dan Zatloukal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Executive Vice President - Head of Asset Management</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/scott-johnson-75230</t>
+          <t>https://linkedin.com/in/dan-zatloukal</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -3151,16 +3151,16 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Portfolio Operations</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -3168,37 +3168,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dave Holeman 2728b614</t>
+          <t>Kristina Stortz 81100692</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Director of Investment Diligence and Structure</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/dave-holeman-2728b614</t>
+          <t>https://linkedin.com/in/kristina-stortz-81100692</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -3237,37 +3237,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Made Setiawan 30188266</t>
+          <t>Ty Rembe 954a4850</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Director of Credit and Collections</t>
+          <t>CFO/Controller</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/made-setiawan-30188266</t>
+          <t>https://linkedin.com/in/ty-rembe-954a4850</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -3306,37 +3306,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mike Parrish A2b95488</t>
+          <t>Harvey Outlaw A50a1325</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Parrish</t>
+          <t>Accounting Manager</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mike-parrish-a2b95488</t>
+          <t>https://linkedin.com/in/harvey-outlaw-a50a1325</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -3375,37 +3375,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paul Meekey A7972413</t>
+          <t>Lenka Freundt 60004121</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Director of Managed Parternships</t>
+          <t>Senior Marketing Manager</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/paul-meekey-a7972413</t>
+          <t>https://linkedin.com/in/lenka-freundt-60004121</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -3444,37 +3444,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Matthew Okmin 1508015</t>
+          <t>Michael Marmolejo Cpa Mba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Okmin</t>
+          <t>Assistant Vice President</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/matthew-okmin-1508015</t>
+          <t>https://linkedin.com/in/michael-marmolejo-cpa-mba-81923438</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -3513,37 +3513,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Melanie Richards 9a23107</t>
+          <t>Nicole Wortman</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Property Manager</t>
+          <t>Senior Vice President Finance/Controller</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/melanie-richards-9a23107</t>
+          <t>https://linkedin.com/in/nicole-wortman-78914281</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -3582,37 +3582,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camille Patterson Ccim 83221519</t>
+          <t>Shawn Thomas B40b5178</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Patterson, CCIM</t>
+          <t>Cash Management Manager</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/camille-patterson-ccim-83221519</t>
+          <t>https://linkedin.com/in/shawn-thomas-b40b5178</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -3651,37 +3651,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Daniel Figard 650a909a</t>
+          <t>Chrisrickett1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Figard</t>
+          <t>Assistant Vice President of Acquisitions Underwriting</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/daniel-figard-650a909a</t>
+          <t>https://linkedin.com/in/chrisrickett1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -3720,37 +3720,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Inland Private Capital</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/inland-real-estate-investment-corp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.inlandprivatecapital.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>David Mordy 781479203</t>
+          <t>Cindy Bueneman 8a79685</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mordy</t>
+          <t>Bueneman</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/david-mordy-781479203</t>
+          <t>https://linkedin.com/in/cindy-bueneman-8a79685</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -3772,11 +3772,11 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -3789,37 +3789,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>David Spagnolo 8a753b14</t>
+          <t>Erick Canedo 386984b5</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spagnolo</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/david-spagnolo-8a753b14</t>
+          <t>https://linkedin.com/in/erick-canedo-386984b5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -3858,37 +3858,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ibrahim Mhawesh</t>
+          <t>Marlene Lees 362aa61a</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Director of Insurance &amp; Lender Relations</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ibrahim-mhawesh</t>
+          <t>https://linkedin.com/in/marlene-lees-362aa61a</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -3927,37 +3927,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mark Cervantes A1207630</t>
+          <t>Suzy Cottle 4076a610</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cervantes</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mark-cervantes-a1207630</t>
+          <t>https://linkedin.com/in/suzy-cottle-4076a610</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -3996,37 +3996,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Scott Hogan A7540911</t>
+          <t>Tricia Pfannkuch</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hogan</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/scott-hogan-a7540911</t>
+          <t>https://linkedin.com/in/tricia-pfannkuch</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -4065,37 +4065,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ted Zeck 3b036713</t>
+          <t>Anthony Challenger A9648aa3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Retired CPA, now just walking and drinking Leinie’s</t>
+          <t>Challenger</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ted-zeck-3b036713</t>
+          <t>https://linkedin.com/in/anthony-challenger-a9648aa3</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -4134,37 +4134,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REIT</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/whitestone-reit</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.whitestonereit.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tim Ng 642b3a7</t>
+          <t>Thomas Voekler 9b87741</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Williams Mullen</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/tim-ng-642b3a7</t>
+          <t>https://linkedin.com/in/thomas-voekler-9b87741</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4213,27 +4213,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brad Butler 898a847</t>
+          <t>Anthony Brown1031</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Experienced VP Regional Director | Real Estate Leasing</t>
+          <t>Financial Professional l 1031 Exchange &amp; DSTs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/brad-butler-898a847</t>
+          <t>https://linkedin.com/in/anthony-brown1031</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="V55" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4282,27 +4282,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Doug Himmel</t>
+          <t>Jack Barry</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Director of Leasing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/doug-himmel</t>
+          <t>https://linkedin.com/in/jack-barry-68941220</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="V56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4351,27 +4351,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jeffrey L 584a452</t>
+          <t>Alancliftoncpm</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vice President - Regional Director Florida</t>
+          <t>Alan Clifton CPM</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/jeffrey-l-584a452</t>
+          <t>https://linkedin.com/in/alancliftoncpm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="V57" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -4410,7 +4410,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4420,27 +4420,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wesrudes</t>
+          <t>Alicia Gregory 8906309b</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Director Of Leasing</t>
+          <t>Assistant General Manager</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/wesrudes</t>
+          <t>https://linkedin.com/in/alicia-gregory-8906309b</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
@@ -4479,7 +4479,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4489,27 +4489,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chris Eckerd Cpm 435a20a8</t>
+          <t>Davidwolke1407</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SVP</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/chris-eckerd-cpm-435a20a8</t>
+          <t>https://linkedin.com/in/davidwolke1407</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="V59" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Portfolio Manager</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4558,27 +4558,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Anthony Pascale Jr</t>
+          <t>Durantecathryn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Director of Financial Reporting</t>
+          <t>Cathryn Durante</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/anthony-pascale-jr</t>
+          <t>https://linkedin.com/in/durantecathryn</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="V60" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -4617,7 +4617,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Erin Grandys</t>
+          <t>Gail Leist 2a8756a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Property Manager skilled in Facility Management and Property Management</t>
+          <t>Manager Marketing Due Diligence</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/erin-grandys</t>
+          <t>https://linkedin.com/in/gail-leist-2a8756a</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -4686,7 +4686,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4696,27 +4696,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>John Beale 810340104</t>
+          <t>Juliekasper</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Senior Property Manager</t>
+          <t>Communications Director</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/john-beale-810340104</t>
+          <t>https://linkedin.com/in/juliekasper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -4738,16 +4738,16 @@
         </is>
       </c>
       <c r="V62" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -4755,7 +4755,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Workspace Property Trust</t>
+          <t>Passco Companies</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4765,27 +4765,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
+          <t>https://www.linkedin.com/company/passco</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.workspacept.com</t>
+          <t>https://www.passco.com</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kevin Ault</t>
+          <t>Colin Gillis 6a1aa95</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Gillis</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/kevin-ault</t>
+          <t>https://linkedin.com/in/colin-gillis-6a1aa95</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -4807,11 +4807,11 @@
         </is>
       </c>
       <c r="V63" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -4820,420 +4820,6 @@
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Workspace Property Trust</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://www.workspacept.com</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Lisa Grace 272121111</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Manager of Lease Administrator and Accounts Recievable</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/lisa-grace-272121111</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>tavily</t>
-        </is>
-      </c>
-      <c r="V64" t="n">
-        <v>70</v>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Workspace Property Trust</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://www.workspacept.com</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Michael Gervasio 658453a5</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Senior Vice President</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/michael-gervasio-658453a5</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>tavily</t>
-        </is>
-      </c>
-      <c r="V65" t="n">
-        <v>70</v>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Workspace Property Trust</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://www.workspacept.com</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Mikaela Sherbakov</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Senior Corporate Accountant</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/mikaela-sherbakov</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>tavily</t>
-        </is>
-      </c>
-      <c r="V66" t="n">
-        <v>70</v>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Workspace Property Trust</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://www.workspacept.com</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Stephanpahides</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>SVP &amp; General Counsel</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/stephanpahides</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>tavily</t>
-        </is>
-      </c>
-      <c r="V67" t="n">
-        <v>65</v>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Workspace Property Trust</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>https://www.workspacept.com</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Edgar Gaba B643a765</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Gaba</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/edgar-gaba-b643a765</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>tavily</t>
-        </is>
-      </c>
-      <c r="V68" t="n">
-        <v>60</v>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Workspace Property Trust</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/workspace-property-trust</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>https://www.workspacept.com</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Francis X Shea 904361116</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Construction &amp; Development Executive</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/francis-x-shea-904361116</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>tavily</t>
-        </is>
-      </c>
-      <c r="V69" t="n">
-        <v>60</v>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Portfolio Manager</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
